--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.95003272787287</v>
+        <v>1.941880318279342</v>
       </c>
       <c r="D2" t="n">
-        <v>25.48770912049251</v>
+        <v>4.141752732080033</v>
       </c>
       <c r="E2" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F2" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.6645819086029</v>
+        <v>3.520494560147971</v>
       </c>
       <c r="D3" t="n">
-        <v>23.58410481659204</v>
+        <v>3.832417032696206</v>
       </c>
       <c r="E3" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F3" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.0397292990407</v>
+        <v>1.631456011094114</v>
       </c>
       <c r="D4" t="n">
-        <v>9.531030488392402</v>
+        <v>1.548792454363765</v>
       </c>
       <c r="E4" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F4" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>0.8125</v>
       </c>
       <c r="D5" t="n">
-        <v>13.90808127613306</v>
+        <v>2.260063207371622</v>
       </c>
       <c r="E5" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F5" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.50861812854691</v>
+        <v>2.357650445888873</v>
       </c>
       <c r="D6" t="n">
-        <v>10.42866428806246</v>
+        <v>1.69465794681015</v>
       </c>
       <c r="E6" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F6" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.40223918376519</v>
+        <v>4.127863867361843</v>
       </c>
       <c r="D7" t="n">
-        <v>20.01235979638382</v>
+        <v>3.25200846691237</v>
       </c>
       <c r="E7" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F7" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.861523573916369</v>
+        <v>1.43999758076141</v>
       </c>
       <c r="D8" t="n">
-        <v>7.24232446942267</v>
+        <v>1.176877726281184</v>
       </c>
       <c r="E8" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F8" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>7.568171263714835</v>
+        <v>1.229827830353661</v>
       </c>
       <c r="D9" t="n">
-        <v>12.68642413953132</v>
+        <v>2.06154392267384</v>
       </c>
       <c r="E9" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F9" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.34571762822613</v>
+        <v>2.168679114586746</v>
       </c>
       <c r="D10" t="n">
-        <v>4.765097498403598</v>
+        <v>0.7743283434905848</v>
       </c>
       <c r="E10" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F10" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.7568164921976</v>
+        <v>2.235482679982111</v>
       </c>
       <c r="D11" t="n">
-        <v>2.331652126261621</v>
+        <v>0.3788934705175135</v>
       </c>
       <c r="E11" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F11" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>5.76949146688194</v>
+        <v>0.9375423633683152</v>
       </c>
       <c r="D12" t="n">
-        <v>16.45364236353177</v>
+        <v>2.673716884073912</v>
       </c>
       <c r="E12" t="n">
-        <v>6.047095903279942</v>
+        <v>0.9826530842829906</v>
       </c>
       <c r="F12" t="n">
-        <v>7.149973453116685</v>
+        <v>1.161870686131461</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
